--- a/data/trans_bre/P38B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,11</t>
+          <t>-3,1; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 10,33</t>
+          <t>0,36; 9,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 8,5</t>
+          <t>0,13; 9,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 7,09</t>
+          <t>-3,34; 7,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 12,49</t>
+          <t>0,46; 11,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 10,37</t>
+          <t>0,14; 11,34</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,37</t>
+          <t>-4,12; 5,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 6,32</t>
+          <t>-3,35; 6,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,79</t>
+          <t>-2,7; 6,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 6,13</t>
+          <t>-4,49; 5,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,45</t>
+          <t>-3,73; 7,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 8,37</t>
+          <t>-3,07; 8,0</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,87</t>
+          <t>1,01; 11,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 7,47</t>
+          <t>-4,34; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 72,75</t>
+          <t>2,69; 70,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,97</t>
+          <t>1,2; 13,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 8,8</t>
+          <t>-4,96; 8,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 373,03</t>
+          <t>3,0; 313,51</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,19</t>
+          <t>-1,85; 5,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 4,81</t>
+          <t>-1,98; 4,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 15,57</t>
+          <t>5,54; 15,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,18</t>
+          <t>-2,12; 6,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 5,81</t>
+          <t>-2,32; 5,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 19,76</t>
+          <t>6,65; 19,65</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 14,13</t>
+          <t>5,17; 13,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,36</t>
+          <t>2,51; 10,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 11,61</t>
+          <t>-18,72; 11,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 18,68</t>
+          <t>6,18; 17,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,12</t>
+          <t>3,08; 14,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 14,66</t>
+          <t>-23,31; 14,99</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,84; 47,3</t>
+          <t>34,29; 47,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,91; 40,04</t>
+          <t>26,67; 39,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,68; 47,55</t>
+          <t>24,52; 47,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67,13; 122,69</t>
+          <t>69,47; 122,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,15; 84,25</t>
+          <t>44,38; 82,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,74; 136,49</t>
+          <t>42,93; 134,67</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,47</t>
+          <t>3,94; 7,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,18</t>
+          <t>3,75; 7,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 32,39</t>
+          <t>4,35; 28,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,25</t>
+          <t>4,75; 9,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,9</t>
+          <t>4,51; 8,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 57,41</t>
+          <t>5,45; 48,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,11</t>
+          <t>-2,84; 6,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 9,63</t>
+          <t>0,84; 10,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 9,21</t>
+          <t>-0,15; 8,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 7,04</t>
+          <t>-3,12; 6,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 11,69</t>
+          <t>0,95; 12,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 11,34</t>
+          <t>-0,25; 10,41</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 5,1</t>
+          <t>-3,64; 5,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,44</t>
+          <t>-3,54; 6,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 6,64</t>
+          <t>-2,84; 7,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,79</t>
+          <t>-3,96; 6,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 7,68</t>
+          <t>-3,99; 7,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 8,0</t>
+          <t>-3,2; 8,68</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36,64</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 11,21</t>
+          <t>1,37; 10,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 7,38</t>
+          <t>-3,85; 7,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 70,13</t>
+          <t>-0,44; 9,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 13,59</t>
+          <t>1,6; 13,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 8,76</t>
+          <t>-4,38; 9,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 313,51</t>
+          <t>-0,48; 11,79</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 5,08</t>
+          <t>-1,47; 5,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,23</t>
+          <t>-1,55; 4,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 15,68</t>
+          <t>3,73; 10,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 6,06</t>
+          <t>-1,68; 6,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,14</t>
+          <t>-1,88; 5,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 19,65</t>
+          <t>4,49; 13,86</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>12,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,82</t>
+          <t>5,17; 13,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,84</t>
+          <t>2,1; 10,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 11,85</t>
+          <t>7,86; 17,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 17,87</t>
+          <t>6,3; 17,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 14,08</t>
+          <t>2,52; 13,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 14,99</t>
+          <t>9,84; 23,47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35,56</t>
+          <t>38,33</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,29; 47,0</t>
+          <t>34,17; 47,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,67; 39,46</t>
+          <t>26,79; 39,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,52; 47,08</t>
+          <t>27,02; 47,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,47; 122,7</t>
+          <t>67,18; 124,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,38; 82,78</t>
+          <t>44,9; 83,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,93; 134,67</t>
+          <t>50,89; 145,95</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,49</t>
+          <t>3,98; 7,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,25</t>
+          <t>3,73; 7,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 28,52</t>
+          <t>4,82; 8,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,18</t>
+          <t>4,77; 9,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,98</t>
+          <t>4,53; 8,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 48,71</t>
+          <t>5,89; 11,37</t>
         </is>
       </c>
     </row>
